--- a/Business - Technology Services/Datacenter/IREN.xlsx
+++ b/Business - Technology Services/Datacenter/IREN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\Business - Technology Services\Datacenter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5799BB-4656-49E9-9C47-BD38F5C2A2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7161583A-C58C-49E3-8DB1-3E7407DED8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2382,7 +2382,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2527,6 +2527,13 @@
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2583,32 +2590,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4532,6 +4513,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5AB5-4DA7-8507-D888923268D3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -4548,6 +4534,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5AB5-4DA7-8507-D888923268D3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -5193,6 +5184,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-0F3E-4E13-8C9C-5F35C0437F60}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -17833,7 +17829,7 @@
       <c r="E3" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F3" s="158">
+      <c r="F3" s="120">
         <v>3.5200000000000002E-2</v>
       </c>
       <c r="H3" t="s">
@@ -17857,7 +17853,7 @@
       <c r="E4" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="158">
+      <c r="F4" s="120">
         <v>2.9700000000000001E-2</v>
       </c>
       <c r="H4" t="s">
@@ -17879,7 +17875,7 @@
       <c r="E5" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="158">
+      <c r="F5" s="120">
         <v>2.6200000000000001E-2</v>
       </c>
       <c r="H5" t="s">
@@ -17905,7 +17901,7 @@
       <c r="E6" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F6" s="158">
+      <c r="F6" s="120">
         <v>2.2200000000000001E-2</v>
       </c>
       <c r="H6" t="s">
@@ -17932,7 +17928,7 @@
       <c r="E7" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F7" s="158">
+      <c r="F7" s="120">
         <v>2.2100000000000002E-2</v>
       </c>
       <c r="H7" t="s">
@@ -17959,7 +17955,7 @@
       <c r="E8" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F8" s="158">
+      <c r="F8" s="120">
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="I8" s="10"/>
@@ -17983,7 +17979,7 @@
       <c r="E9" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F9" s="158">
+      <c r="F9" s="120">
         <v>1.6799999999999999E-2</v>
       </c>
       <c r="I9" s="10"/>
@@ -18007,7 +18003,7 @@
       <c r="E10" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F10" s="158">
+      <c r="F10" s="120">
         <v>1.35E-2</v>
       </c>
       <c r="I10" s="10"/>
@@ -18031,7 +18027,7 @@
       <c r="E11" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F11" s="158">
+      <c r="F11" s="120">
         <v>1.26E-2</v>
       </c>
       <c r="I11" s="10"/>
@@ -18050,7 +18046,7 @@
       <c r="E12" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F12" s="158">
+      <c r="F12" s="120">
         <v>1.09E-2</v>
       </c>
       <c r="J12" s="13"/>
@@ -18066,7 +18062,7 @@
         <v>142.51361433747414</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="158"/>
+      <c r="F13" s="120"/>
       <c r="J13" s="13"/>
       <c r="L13" s="5"/>
       <c r="N13" s="13"/>
@@ -18118,11 +18114,11 @@
       <c r="E17" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="L17" s="116" t="s">
+      <c r="L17" s="121" t="s">
         <v>174</v>
       </c>
-      <c r="M17" s="117"/>
-      <c r="N17" s="118"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="123"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
@@ -18132,9 +18128,9 @@
         <f>C14/(C16*100)</f>
         <v>25.63588116583113</v>
       </c>
-      <c r="L18" s="119"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="121"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="126"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
@@ -18144,9 +18140,9 @@
         <f>C15/(C17*100)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L19" s="119"/>
-      <c r="M19" s="120"/>
-      <c r="N19" s="121"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="125"/>
+      <c r="N19" s="126"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -18156,9 +18152,9 @@
         <f>Model!F6/Model!E5-1</f>
         <v>0.8801532065394202</v>
       </c>
-      <c r="L20" s="119"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="121"/>
+      <c r="L20" s="124"/>
+      <c r="M20" s="125"/>
+      <c r="N20" s="126"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
@@ -18168,9 +18164,9 @@
         <f>Model!G6/Model!F6-1</f>
         <v>2.0042462845010616</v>
       </c>
-      <c r="L21" s="119"/>
-      <c r="M21" s="120"/>
-      <c r="N21" s="121"/>
+      <c r="L21" s="124"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="126"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
@@ -18180,9 +18176,9 @@
         <f>Model!E26</f>
         <v>93.5</v>
       </c>
-      <c r="L22" s="119"/>
-      <c r="M22" s="120"/>
-      <c r="N22" s="121"/>
+      <c r="L22" s="124"/>
+      <c r="M22" s="125"/>
+      <c r="N22" s="126"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
@@ -18192,9 +18188,9 @@
         <f>Model!E26</f>
         <v>93.5</v>
       </c>
-      <c r="L23" s="119"/>
-      <c r="M23" s="120"/>
-      <c r="N23" s="121"/>
+      <c r="L23" s="124"/>
+      <c r="M23" s="125"/>
+      <c r="N23" s="126"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
@@ -18204,9 +18200,9 @@
         <f>Model!E32</f>
         <v>0.68266526686399631</v>
       </c>
-      <c r="L24" s="119"/>
-      <c r="M24" s="120"/>
-      <c r="N24" s="121"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="125"/>
+      <c r="N24" s="126"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
@@ -18216,9 +18212,9 @@
         <f>Model!E33</f>
         <v>0.17352496791564459</v>
       </c>
-      <c r="L25" s="119"/>
-      <c r="M25" s="120"/>
-      <c r="N25" s="121"/>
+      <c r="L25" s="124"/>
+      <c r="M25" s="125"/>
+      <c r="N25" s="126"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
@@ -18228,9 +18224,9 @@
         <f>C12/Model!E26</f>
         <v>182.4522487486631</v>
       </c>
-      <c r="L26" s="119"/>
-      <c r="M26" s="120"/>
-      <c r="N26" s="121"/>
+      <c r="L26" s="124"/>
+      <c r="M26" s="125"/>
+      <c r="N26" s="126"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
@@ -18243,9 +18239,9 @@
       <c r="E27" t="s">
         <v>56</v>
       </c>
-      <c r="L27" s="119"/>
-      <c r="M27" s="120"/>
-      <c r="N27" s="121"/>
+      <c r="L27" s="124"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="126"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
@@ -18255,9 +18251,9 @@
         <f>Model!E26/(-Model!E18)</f>
         <v>12.460021321961621</v>
       </c>
-      <c r="L28" s="122"/>
-      <c r="M28" s="123"/>
-      <c r="N28" s="124"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="129"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
@@ -18418,9 +18414,7 @@
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="135"/>
     <col min="5" max="5" width="11.42578125" style="13"/>
-    <col min="16" max="16" width="11.42578125" style="135"/>
     <col min="19" max="19" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
@@ -18428,7 +18422,7 @@
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="151">
+      <c r="P1" s="12">
         <v>45747</v>
       </c>
       <c r="Q1" s="12">
@@ -18457,7 +18451,7 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="135" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="13" t="s">
@@ -18487,7 +18481,7 @@
       <c r="O2" t="s">
         <v>130</v>
       </c>
-      <c r="P2" s="135" t="s">
+      <c r="P2" t="s">
         <v>131</v>
       </c>
       <c r="Q2" t="s">
@@ -18499,10 +18493,10 @@
       <c r="S2" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="T2" s="144" t="s">
+      <c r="T2" t="s">
         <v>136</v>
       </c>
-      <c r="U2" s="144" t="s">
+      <c r="U2" t="s">
         <v>137</v>
       </c>
     </row>
@@ -18511,7 +18505,7 @@
         <v>153</v>
       </c>
       <c r="C3" s="10"/>
-      <c r="D3" s="138">
+      <c r="D3" s="10">
         <v>184.08699999999999</v>
       </c>
       <c r="E3" s="15">
@@ -18529,7 +18523,7 @@
       <c r="O3" s="10">
         <v>113.483</v>
       </c>
-      <c r="P3" s="138"/>
+      <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10">
         <v>232.94800000000001</v>
@@ -18537,15 +18531,15 @@
       <c r="S3" s="15">
         <v>167.39400000000001</v>
       </c>
-      <c r="T3" s="138"/>
-      <c r="U3" s="138"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>154</v>
       </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="138">
+      <c r="D4" s="10">
         <v>3.105</v>
       </c>
       <c r="E4" s="15">
@@ -18563,7 +18557,7 @@
       <c r="O4" s="10">
         <v>2.661</v>
       </c>
-      <c r="P4" s="138"/>
+      <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10">
         <v>7.3470000000000004</v>
@@ -18571,8 +18565,8 @@
       <c r="S4" s="15">
         <v>17.297999999999998</v>
       </c>
-      <c r="T4" s="138"/>
-      <c r="U4" s="138"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
     </row>
     <row r="5" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
@@ -18582,7 +18576,7 @@
         <f>SUM(C3:C4)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="136">
+      <c r="D5" s="11">
         <f>SUM(D3:D4)</f>
         <v>187.19199999999998</v>
       </c>
@@ -18595,51 +18589,51 @@
         <v>0</v>
       </c>
       <c r="J5" s="11">
-        <f>SUM(J3:J4)</f>
+        <f t="shared" ref="J5:U5" si="0">SUM(J3:J4)</f>
         <v>0</v>
       </c>
       <c r="K5" s="11">
-        <f>SUM(K3:K4)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L5" s="11">
-        <f>SUM(L3:L4)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M5" s="11">
-        <f>SUM(M3:M4)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N5" s="11">
-        <f>SUM(N3:N4)</f>
+        <f t="shared" si="0"/>
         <v>52.764000000000003</v>
       </c>
       <c r="O5" s="11">
-        <f>SUM(O3:O4)</f>
+        <f t="shared" si="0"/>
         <v>116.14400000000001</v>
       </c>
-      <c r="P5" s="136">
-        <f>SUM(P3:P4)</f>
+      <c r="P5" s="11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q5" s="11">
-        <f>SUM(Q3:Q4)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R5" s="11">
-        <f>SUM(R3:R4)</f>
+        <f t="shared" si="0"/>
         <v>240.29500000000002</v>
       </c>
       <c r="S5" s="14">
-        <f>SUM(S3:S4)</f>
+        <f t="shared" si="0"/>
         <v>184.69200000000001</v>
       </c>
-      <c r="T5" s="136">
-        <f>SUM(T3:T4)</f>
+      <c r="T5" s="11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U5" s="136">
-        <f>SUM(U3:U4)</f>
+      <c r="U5" s="11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -18648,8 +18642,8 @@
         <v>48</v>
       </c>
       <c r="C6" s="10"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="146"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="117"/>
       <c r="F6" s="115">
         <v>942</v>
       </c>
@@ -18662,26 +18656,26 @@
       <c r="M6" s="39"/>
       <c r="N6" s="39"/>
       <c r="O6" s="39"/>
-      <c r="P6" s="137"/>
+      <c r="P6" s="39"/>
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="110"/>
-      <c r="T6" s="137">
+      <c r="T6" s="39">
         <v>220</v>
       </c>
-      <c r="U6" s="137">
+      <c r="U6" s="39">
         <v>315</v>
       </c>
       <c r="V6">
         <v>520</v>
       </c>
-      <c r="W6" s="156">
+      <c r="W6" s="39">
         <v>738</v>
       </c>
-      <c r="X6" s="156">
+      <c r="X6" s="39">
         <v>912</v>
       </c>
-      <c r="Y6" s="156">
+      <c r="Y6" s="39">
         <v>1000</v>
       </c>
     </row>
@@ -18690,13 +18684,12 @@
         <v>155</v>
       </c>
       <c r="C7" s="10"/>
-      <c r="D7" s="137">
+      <c r="D7" s="39">
         <v>86.668000000000006</v>
       </c>
-      <c r="E7" s="149">
+      <c r="E7" s="110">
         <v>157.673</v>
       </c>
-      <c r="F7" s="150"/>
       <c r="J7" s="39"/>
       <c r="K7" s="39"/>
       <c r="L7" s="39"/>
@@ -18707,7 +18700,7 @@
       <c r="O7" s="39">
         <v>32.018999999999998</v>
       </c>
-      <c r="P7" s="137"/>
+      <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
       <c r="R7" s="39">
         <v>79.944999999999993</v>
@@ -18715,21 +18708,20 @@
       <c r="S7" s="110">
         <v>63.368000000000002</v>
       </c>
-      <c r="T7" s="137"/>
-      <c r="U7" s="137"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>154</v>
       </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="137">
+      <c r="D8" s="39">
         <v>0.379</v>
       </c>
-      <c r="E8" s="149">
+      <c r="E8" s="110">
         <v>1.319</v>
       </c>
-      <c r="F8" s="150"/>
       <c r="J8" s="39"/>
       <c r="K8" s="39"/>
       <c r="L8" s="39"/>
@@ -18740,7 +18732,7 @@
       <c r="O8" s="39">
         <v>0.27500000000000002</v>
       </c>
-      <c r="P8" s="137"/>
+      <c r="P8" s="39"/>
       <c r="Q8" s="39"/>
       <c r="R8" s="39">
         <v>0.72799999999999998</v>
@@ -18748,8 +18740,8 @@
       <c r="S8" s="110">
         <v>2.395</v>
       </c>
-      <c r="T8" s="137"/>
-      <c r="U8" s="137"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
     </row>
     <row r="9" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
@@ -18759,7 +18751,7 @@
         <f>SUM(C7:C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="136">
+      <c r="D9" s="11">
         <f>SUM(D7:D8)</f>
         <v>87.047000000000011</v>
       </c>
@@ -18772,51 +18764,51 @@
         <v>0</v>
       </c>
       <c r="J9" s="11">
-        <f>SUM(J7:J8)</f>
+        <f t="shared" ref="J9:U9" si="1">SUM(J7:J8)</f>
         <v>0</v>
       </c>
       <c r="K9" s="11">
-        <f>SUM(K7:K8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L9" s="11">
-        <f>SUM(L7:L8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M9" s="11">
-        <f>SUM(M7:M8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N9" s="11">
-        <f>SUM(N7:N8)</f>
+        <f t="shared" si="1"/>
         <v>31.858999999999998</v>
       </c>
       <c r="O9" s="11">
-        <f>SUM(O7:O8)</f>
+        <f t="shared" si="1"/>
         <v>32.293999999999997</v>
       </c>
-      <c r="P9" s="136">
-        <f>SUM(P7:P8)</f>
+      <c r="P9" s="11">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q9" s="11">
-        <f>SUM(Q7:Q8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R9" s="11">
-        <f>SUM(R7:R8)</f>
+        <f t="shared" si="1"/>
         <v>80.672999999999988</v>
       </c>
       <c r="S9" s="14">
-        <f>SUM(S7:S8)</f>
+        <f t="shared" si="1"/>
         <v>65.763000000000005</v>
       </c>
-      <c r="T9" s="136">
-        <f>SUM(T7:T8)</f>
+      <c r="T9" s="11">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U9" s="136">
-        <f>SUM(U7:U8)</f>
+      <c r="U9" s="11">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -18825,7 +18817,7 @@
         <v>156</v>
       </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="137">
+      <c r="D10" s="39">
         <v>70.424000000000007</v>
       </c>
       <c r="E10" s="110">
@@ -18841,7 +18833,7 @@
       <c r="O10" s="10">
         <v>28.891999999999999</v>
       </c>
-      <c r="P10" s="138"/>
+      <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10">
         <v>138.35900000000001</v>
@@ -18849,15 +18841,15 @@
       <c r="S10" s="15">
         <v>100.755</v>
       </c>
-      <c r="T10" s="138"/>
-      <c r="U10" s="138"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>157</v>
       </c>
       <c r="C11" s="10"/>
-      <c r="D11" s="137">
+      <c r="D11" s="39">
         <v>50.47</v>
       </c>
       <c r="E11" s="110">
@@ -18873,7 +18865,7 @@
       <c r="O11" s="10">
         <v>36.076999999999998</v>
       </c>
-      <c r="P11" s="138"/>
+      <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="10">
         <v>85.225999999999999</v>
@@ -18881,15 +18873,15 @@
       <c r="S11" s="15">
         <v>99.176000000000002</v>
       </c>
-      <c r="T11" s="138"/>
-      <c r="U11" s="138"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>158</v>
       </c>
       <c r="C12" s="10"/>
-      <c r="D12" s="138">
+      <c r="D12" s="10">
         <v>0</v>
       </c>
       <c r="E12" s="15">
@@ -18905,7 +18897,7 @@
       <c r="O12" s="10">
         <v>0</v>
       </c>
-      <c r="P12" s="138"/>
+      <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10">
         <v>16.257000000000001</v>
@@ -18913,15 +18905,15 @@
       <c r="S12" s="15">
         <v>31.754999999999999</v>
       </c>
-      <c r="T12" s="138"/>
-      <c r="U12" s="138"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>159</v>
       </c>
       <c r="C13" s="10"/>
-      <c r="D13" s="138">
+      <c r="D13" s="10">
         <v>-4.2999999999999997E-2</v>
       </c>
       <c r="E13" s="15">
@@ -18937,7 +18929,7 @@
       <c r="O13" s="10">
         <v>0.68100000000000005</v>
       </c>
-      <c r="P13" s="138"/>
+      <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10">
         <v>1.2999999999999999E-2</v>
@@ -18945,15 +18937,15 @@
       <c r="S13" s="15">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="T13" s="138"/>
-      <c r="U13" s="138"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>160</v>
       </c>
       <c r="C14" s="10"/>
-      <c r="D14" s="138">
+      <c r="D14" s="10">
         <v>8.0739999999999998</v>
       </c>
       <c r="E14" s="15">
@@ -18969,7 +18961,7 @@
       <c r="O14" s="10">
         <v>3.9940000000000002</v>
       </c>
-      <c r="P14" s="138"/>
+      <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="10">
         <v>0</v>
@@ -18977,15 +18969,15 @@
       <c r="S14" s="15">
         <v>5.468</v>
       </c>
-      <c r="T14" s="138"/>
-      <c r="U14" s="138"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>161</v>
       </c>
       <c r="C15" s="10"/>
-      <c r="D15" s="137">
+      <c r="D15" s="39">
         <v>-1.5660000000000001</v>
       </c>
       <c r="E15" s="110">
@@ -19001,7 +18993,7 @@
       <c r="O15" s="10">
         <v>-3.1040000000000001</v>
       </c>
-      <c r="P15" s="138"/>
+      <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10">
         <v>-3.8279999999999998</v>
@@ -19009,8 +19001,8 @@
       <c r="S15" s="15">
         <v>-1.8149999999999999</v>
       </c>
-      <c r="T15" s="138"/>
-      <c r="U15" s="138"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
     </row>
     <row r="16" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
@@ -19020,7 +19012,7 @@
         <f>C5-SUM(C9:C15)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="136">
+      <c r="D16" s="11">
         <f>D5-SUM(D9:D15)</f>
         <v>-27.214000000000027</v>
       </c>
@@ -19036,51 +19028,51 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11">
-        <f>J5-SUM(J9:J15)</f>
+        <f t="shared" ref="J16:U16" si="2">J5-SUM(J9:J15)</f>
         <v>0</v>
       </c>
       <c r="K16" s="11">
-        <f>K5-SUM(K9:K15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="11">
-        <f>L5-SUM(L9:L15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M16" s="11">
-        <f>M5-SUM(M9:M15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N16" s="11">
-        <f>N5-SUM(N9:N15)</f>
+        <f t="shared" si="2"/>
         <v>-47.085999999999991</v>
       </c>
       <c r="O16" s="11">
-        <f>O5-SUM(O9:O15)</f>
+        <f t="shared" si="2"/>
         <v>17.310000000000016</v>
       </c>
-      <c r="P16" s="136">
-        <f>P5-SUM(P9:P15)</f>
+      <c r="P16" s="11">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q16" s="11">
-        <f>Q5-SUM(Q9:Q15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R16" s="11">
-        <f>R5-SUM(R9:R15)</f>
+        <f t="shared" si="2"/>
         <v>-76.404999999999973</v>
       </c>
       <c r="S16" s="14">
-        <f>S5-SUM(S9:S15)</f>
+        <f t="shared" si="2"/>
         <v>-116.40300000000002</v>
       </c>
-      <c r="T16" s="136">
-        <f>T5-SUM(T9:T15)</f>
+      <c r="T16" s="11">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U16" s="136">
-        <f>U5-SUM(U9:U15)</f>
+      <c r="U16" s="11">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -19089,7 +19081,7 @@
         <v>162</v>
       </c>
       <c r="C17" s="10"/>
-      <c r="D17" s="138">
+      <c r="D17" s="10">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="E17" s="15">
@@ -19106,7 +19098,7 @@
       <c r="O17" s="10">
         <v>1.722</v>
       </c>
-      <c r="P17" s="138"/>
+      <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10">
         <v>9.2799999999999994</v>
@@ -19114,15 +19106,15 @@
       <c r="S17" s="15">
         <v>10.667999999999999</v>
       </c>
-      <c r="T17" s="138"/>
-      <c r="U17" s="138"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>163</v>
       </c>
       <c r="C18" s="10"/>
-      <c r="D18" s="138">
+      <c r="D18" s="10">
         <v>-5.8310000000000004</v>
       </c>
       <c r="E18" s="15">
@@ -19139,7 +19131,7 @@
       <c r="O18" s="10">
         <v>-1.587</v>
       </c>
-      <c r="P18" s="138"/>
+      <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10">
         <v>-7.1280000000000001</v>
@@ -19147,15 +19139,15 @@
       <c r="S18" s="15">
         <v>-15.775</v>
       </c>
-      <c r="T18" s="138"/>
-      <c r="U18" s="138"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>164</v>
       </c>
       <c r="C19" s="10"/>
-      <c r="D19" s="138">
+      <c r="D19" s="10">
         <v>0</v>
       </c>
       <c r="E19" s="15">
@@ -19172,7 +19164,7 @@
       <c r="O19" s="10">
         <v>-0.51600000000000001</v>
       </c>
-      <c r="P19" s="138"/>
+      <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10">
         <v>0</v>
@@ -19180,15 +19172,15 @@
       <c r="S19" s="15">
         <v>6.4489999999999998</v>
       </c>
-      <c r="T19" s="138"/>
-      <c r="U19" s="138"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>166</v>
       </c>
       <c r="C20" s="10"/>
-      <c r="D20" s="138">
+      <c r="D20" s="10">
         <v>-4.1210000000000004</v>
       </c>
       <c r="E20" s="15">
@@ -19205,7 +19197,7 @@
       <c r="O20" s="10">
         <v>0</v>
       </c>
-      <c r="P20" s="138"/>
+      <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10">
         <v>5.7560000000000002</v>
@@ -19213,15 +19205,15 @@
       <c r="S20" s="15">
         <v>2.91</v>
       </c>
-      <c r="T20" s="138"/>
-      <c r="U20" s="138"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>165</v>
       </c>
       <c r="C21" s="10"/>
-      <c r="D21" s="138">
+      <c r="D21" s="10">
         <v>3.448</v>
       </c>
       <c r="E21" s="15">
@@ -19238,7 +19230,7 @@
       <c r="O21" s="10">
         <v>32.299999999999997</v>
       </c>
-      <c r="P21" s="138"/>
+      <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="10">
         <v>-664.99300000000005</v>
@@ -19246,15 +19238,15 @@
       <c r="S21" s="15">
         <v>107.351</v>
       </c>
-      <c r="T21" s="138"/>
-      <c r="U21" s="138"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>167</v>
       </c>
       <c r="C22" s="10"/>
-      <c r="D22" s="138">
+      <c r="D22" s="10">
         <v>0</v>
       </c>
       <c r="E22" s="15">
@@ -19269,7 +19261,7 @@
       <c r="O22" s="10">
         <v>0</v>
       </c>
-      <c r="P22" s="138"/>
+      <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
       <c r="R22" s="10">
         <v>5.3819999999999997</v>
@@ -19277,15 +19269,15 @@
       <c r="S22" s="15">
         <v>0</v>
       </c>
-      <c r="T22" s="138"/>
-      <c r="U22" s="138"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>170</v>
       </c>
       <c r="C23" s="10"/>
-      <c r="D23" s="138">
+      <c r="D23" s="10">
         <v>0</v>
       </c>
       <c r="E23" s="15">
@@ -19300,21 +19292,21 @@
       <c r="O23" s="10">
         <v>0</v>
       </c>
-      <c r="P23" s="138"/>
+      <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="15">
         <v>111.79900000000001</v>
       </c>
-      <c r="T23" s="138"/>
-      <c r="U23" s="138"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>168</v>
       </c>
       <c r="C24" s="10"/>
-      <c r="D24" s="138">
+      <c r="D24" s="10">
         <v>4.7469999999999999</v>
       </c>
       <c r="E24" s="15">
@@ -19331,7 +19323,7 @@
       <c r="O24" s="10">
         <v>4.5629999999999997</v>
       </c>
-      <c r="P24" s="138"/>
+      <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="10">
         <v>0</v>
@@ -19339,15 +19331,15 @@
       <c r="S24" s="15">
         <v>-1.8779999999999999</v>
       </c>
-      <c r="T24" s="138"/>
-      <c r="U24" s="138"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="10"/>
-      <c r="D25" s="138">
+      <c r="D25" s="10">
         <v>-0.108</v>
       </c>
       <c r="E25" s="15">
@@ -19364,24 +19356,24 @@
       <c r="O25" s="10">
         <v>-0.28899999999999998</v>
       </c>
-      <c r="P25" s="138"/>
+      <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="15">
         <v>0</v>
       </c>
-      <c r="T25" s="138"/>
-      <c r="U25" s="138"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
     </row>
     <row r="26" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="136">
+      <c r="C26" s="11">
         <f>C16-SUM(C17:C25)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="136">
+      <c r="D26" s="11">
         <f>D16-SUM(D17:D25)</f>
         <v>-25.447000000000028</v>
       </c>
@@ -19389,159 +19381,158 @@
         <f>E16-SUM(E17:E25)</f>
         <v>93.5</v>
       </c>
-      <c r="F26" s="136">
+      <c r="F26" s="11">
         <f>F16-SUM(F17:F25)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="136">
-        <f t="shared" ref="J26:U26" si="0">J16-SUM(J17:J25)</f>
+      <c r="J26" s="11">
+        <f t="shared" ref="J26:U26" si="3">J16-SUM(J17:J25)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="136">
-        <f t="shared" si="0"/>
+      <c r="K26" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L26" s="136">
-        <f t="shared" si="0"/>
+      <c r="L26" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M26" s="136">
-        <f t="shared" si="0"/>
+      <c r="M26" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N26" s="136">
-        <f t="shared" si="0"/>
+      <c r="N26" s="11">
+        <f t="shared" si="3"/>
         <v>-50.375999999999991</v>
       </c>
-      <c r="O26" s="136">
-        <f t="shared" si="0"/>
+      <c r="O26" s="11">
+        <f t="shared" si="3"/>
         <v>-18.882999999999981</v>
       </c>
-      <c r="P26" s="136">
-        <f t="shared" si="0"/>
+      <c r="P26" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="136">
-        <f t="shared" si="0"/>
+      <c r="Q26" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R26" s="136">
-        <f t="shared" si="0"/>
+      <c r="R26" s="11">
+        <f t="shared" si="3"/>
         <v>575.29800000000012</v>
       </c>
       <c r="S26" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-337.92700000000002</v>
       </c>
-      <c r="T26" s="136">
-        <f t="shared" si="0"/>
+      <c r="T26" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U26" s="136">
-        <f t="shared" si="0"/>
+      <c r="U26" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:25" s="152" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="152" t="s">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="153"/>
-      <c r="D27" s="154">
+      <c r="C27" s="10"/>
+      <c r="D27" s="10">
         <v>3.4529999999999998</v>
       </c>
-      <c r="E27" s="155">
+      <c r="E27" s="15">
         <v>6.56</v>
       </c>
-      <c r="F27" s="153"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="153"/>
-      <c r="M27" s="153"/>
-      <c r="N27" s="153">
+      <c r="F27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10">
         <v>1.282</v>
       </c>
-      <c r="O27" s="153">
+      <c r="O27" s="10">
         <v>3.0049999999999999</v>
       </c>
-      <c r="P27" s="154"/>
-      <c r="Q27" s="153"/>
-      <c r="R27" s="153">
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10">
         <v>190.68700000000001</v>
       </c>
-      <c r="S27" s="155">
+      <c r="S27" s="15">
         <v>-182.52</v>
       </c>
-      <c r="T27" s="154"/>
-      <c r="U27" s="154"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
     </row>
     <row r="28" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="136">
-        <f t="shared" ref="C28:D28" si="1">C26-SUM(C27:C27)</f>
+      <c r="C28" s="11">
+        <f t="shared" ref="C28:D28" si="4">C26-SUM(C27:C27)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="136">
-        <f t="shared" si="1"/>
+      <c r="D28" s="11">
+        <f t="shared" si="4"/>
         <v>-28.900000000000027</v>
       </c>
       <c r="E28" s="14">
         <f>E26-SUM(E27:E27)</f>
         <v>86.94</v>
       </c>
-      <c r="F28" s="136">
+      <c r="F28" s="11">
         <f>F26-SUM(F27:F27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="142"/>
-      <c r="J28" s="136">
-        <f t="shared" ref="J28" si="2">J26-SUM(J27:J27)</f>
+      <c r="J28" s="11">
+        <f t="shared" ref="J28" si="5">J26-SUM(J27:J27)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="136">
-        <f t="shared" ref="K28" si="3">K26-SUM(K27:K27)</f>
+      <c r="K28" s="11">
+        <f t="shared" ref="K28" si="6">K26-SUM(K27:K27)</f>
         <v>0</v>
       </c>
-      <c r="L28" s="136">
-        <f t="shared" ref="L28" si="4">L26-SUM(L27:L27)</f>
+      <c r="L28" s="11">
+        <f t="shared" ref="L28" si="7">L26-SUM(L27:L27)</f>
         <v>0</v>
       </c>
-      <c r="M28" s="136">
-        <f t="shared" ref="M28" si="5">M26-SUM(M27:M27)</f>
+      <c r="M28" s="11">
+        <f t="shared" ref="M28" si="8">M26-SUM(M27:M27)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="136">
-        <f t="shared" ref="N28" si="6">N26-SUM(N27:N27)</f>
+      <c r="N28" s="11">
+        <f t="shared" ref="N28" si="9">N26-SUM(N27:N27)</f>
         <v>-51.657999999999987</v>
       </c>
-      <c r="O28" s="136">
-        <f t="shared" ref="O28" si="7">O26-SUM(O27:O27)</f>
+      <c r="O28" s="11">
+        <f t="shared" ref="O28" si="10">O26-SUM(O27:O27)</f>
         <v>-21.88799999999998</v>
       </c>
-      <c r="P28" s="136">
-        <f t="shared" ref="P28" si="8">P26-SUM(P27:P27)</f>
+      <c r="P28" s="11">
+        <f t="shared" ref="P28" si="11">P26-SUM(P27:P27)</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="136">
-        <f t="shared" ref="Q28" si="9">Q26-SUM(Q27:Q27)</f>
+      <c r="Q28" s="11">
+        <f t="shared" ref="Q28" si="12">Q26-SUM(Q27:Q27)</f>
         <v>0</v>
       </c>
-      <c r="R28" s="136">
-        <f t="shared" ref="R28" si="10">R26-SUM(R27:R27)</f>
+      <c r="R28" s="11">
+        <f t="shared" ref="R28" si="13">R26-SUM(R27:R27)</f>
         <v>384.6110000000001</v>
       </c>
       <c r="S28" s="14">
-        <f t="shared" ref="S28" si="11">S26-SUM(S27:S27)</f>
+        <f t="shared" ref="S28" si="14">S26-SUM(S27:S27)</f>
         <v>-155.40700000000001</v>
       </c>
-      <c r="T28" s="136">
-        <f t="shared" ref="T28" si="12">T26-SUM(T27:T27)</f>
+      <c r="T28" s="11">
+        <f t="shared" ref="T28" si="15">T26-SUM(T27:T27)</f>
         <v>0</v>
       </c>
-      <c r="U28" s="136">
-        <f t="shared" ref="U28" si="13">U26-SUM(U27:U27)</f>
+      <c r="U28" s="11">
+        <f t="shared" ref="U28" si="16">U26-SUM(U27:U27)</f>
         <v>0</v>
       </c>
     </row>
@@ -19550,7 +19541,7 @@
         <v>169</v>
       </c>
       <c r="C29" s="10"/>
-      <c r="D29" s="138">
+      <c r="D29" s="10">
         <v>99.409199999999998</v>
       </c>
       <c r="E29" s="15">
@@ -19567,7 +19558,7 @@
       <c r="O29" s="10">
         <v>210.47018600000001</v>
       </c>
-      <c r="P29" s="138"/>
+      <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="10">
         <v>361.68059299999999</v>
@@ -19575,8 +19566,8 @@
       <c r="S29" s="15">
         <v>298.027356</v>
       </c>
-      <c r="T29" s="138"/>
-      <c r="U29" s="138"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
     </row>
     <row r="30" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -19586,64 +19577,64 @@
         <f>C28/C29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D30" s="139">
-        <f t="shared" ref="D30:F30" si="14">D28/D29</f>
+      <c r="D30" s="2">
+        <f t="shared" ref="D30:F30" si="17">D28/D29</f>
         <v>-0.29071755934058446</v>
       </c>
       <c r="E30" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.38943647775696194</v>
       </c>
       <c r="F30" s="2" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J30" s="2" t="e">
-        <f t="shared" ref="J30:L30" si="15">J28/J29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L30" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="2" t="e">
-        <f t="shared" ref="M30:O30" si="16">M28/M29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" s="2">
-        <f t="shared" si="16"/>
-        <v>-0.2729437393356749</v>
-      </c>
-      <c r="O30" s="2">
-        <f t="shared" si="16"/>
-        <v>-0.10399572697674139</v>
-      </c>
-      <c r="P30" s="139" t="e">
-        <f t="shared" ref="P30:S30" si="17">P28/P29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q30" s="2" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="J30" s="2" t="e">
+        <f t="shared" ref="J30:L30" si="18">J28/J29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" s="2" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L30" s="2" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M30" s="2" t="e">
+        <f t="shared" ref="M30:O30" si="19">M28/M29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" s="2">
+        <f t="shared" si="19"/>
+        <v>-0.2729437393356749</v>
+      </c>
+      <c r="O30" s="2">
+        <f t="shared" si="19"/>
+        <v>-0.10399572697674139</v>
+      </c>
+      <c r="P30" s="2" t="e">
+        <f t="shared" ref="P30:S30" si="20">P28/P29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q30" s="2" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="R30" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>1.0633996057399744</v>
       </c>
       <c r="S30" s="34">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-0.52145213139427382</v>
       </c>
-      <c r="T30" s="139" t="e">
-        <f t="shared" ref="T30:U30" si="18">T28/T29</f>
+      <c r="T30" s="2" t="e">
+        <f t="shared" ref="T30:U30" si="21">T28/T29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U30" s="139" t="e">
-        <f t="shared" si="18"/>
+      <c r="U30" s="2" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19652,8 +19643,8 @@
         <v>47</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="145"/>
-      <c r="E31" s="147"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="118"/>
       <c r="F31" s="1">
         <v>0.41</v>
       </c>
@@ -19666,14 +19657,14 @@
       <c r="M31" s="41"/>
       <c r="N31" s="41"/>
       <c r="O31" s="41"/>
-      <c r="P31" s="140"/>
+      <c r="P31" s="41"/>
       <c r="Q31" s="41"/>
       <c r="R31" s="41"/>
       <c r="S31" s="111"/>
-      <c r="T31" s="140">
+      <c r="T31" s="41">
         <v>-0.22</v>
       </c>
-      <c r="U31" s="140">
+      <c r="U31" s="41">
         <v>-0.1</v>
       </c>
       <c r="V31" s="1">
@@ -19710,51 +19701,51 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J32" s="3" t="e">
-        <f>1-J9/J5</f>
+        <f t="shared" ref="J32:U32" si="22">1-J9/J5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K32" s="38" t="e">
-        <f>1-K9/K5</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L32" s="3" t="e">
-        <f>1-L9/L5</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M32" s="38" t="e">
-        <f>1-M9/M5</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N32" s="3">
-        <f>1-N9/N5</f>
+        <f t="shared" si="22"/>
         <v>0.39619816541581387</v>
       </c>
       <c r="O32" s="3">
-        <f>1-O9/O5</f>
+        <f t="shared" si="22"/>
         <v>0.72194861551177847</v>
       </c>
       <c r="P32" s="38" t="e">
-        <f>1-P9/P5</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q32" s="3" t="e">
-        <f>1-Q9/Q5</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R32" s="3">
-        <f>1-R9/R5</f>
+        <f t="shared" si="22"/>
         <v>0.66427516178031176</v>
       </c>
       <c r="S32" s="6">
-        <f>1-S9/S5</f>
+        <f t="shared" si="22"/>
         <v>0.64393151841985574</v>
       </c>
       <c r="T32" s="38" t="e">
-        <f>1-T9/T5</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U32" s="38" t="e">
-        <f>1-U9/U5</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19766,7 +19757,7 @@
         <f>C28/C5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D33" s="141">
+      <c r="D33" s="4">
         <f>D28/D5</f>
         <v>-0.15438693961280411</v>
       </c>
@@ -19779,51 +19770,51 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J33" s="4" t="e">
-        <f>J28/J5</f>
+        <f t="shared" ref="J33:U33" si="23">J28/J5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="4" t="e">
-        <f>K28/K5</f>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L33" s="4" t="e">
-        <f>L28/L5</f>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M33" s="4" t="e">
-        <f>M28/M5</f>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N33" s="4">
-        <f>N28/N5</f>
+        <f t="shared" si="23"/>
         <v>-0.97903873853384848</v>
       </c>
       <c r="O33" s="4">
-        <f>O28/O5</f>
+        <f t="shared" si="23"/>
         <v>-0.18845571015291346</v>
       </c>
-      <c r="P33" s="141" t="e">
-        <f>P28/P5</f>
+      <c r="P33" s="4" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q33" s="4" t="e">
-        <f>Q28/Q5</f>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R33" s="4">
-        <f>R28/R5</f>
+        <f t="shared" si="23"/>
         <v>1.6005784556482661</v>
       </c>
       <c r="S33" s="7">
-        <f>S28/S5</f>
+        <f t="shared" si="23"/>
         <v>-0.84143871959803351</v>
       </c>
-      <c r="T33" s="141" t="e">
-        <f>T28/T5</f>
+      <c r="T33" s="4" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U33" s="141" t="e">
-        <f>U28/U5</f>
+      <c r="U33" s="4" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19865,50 +19856,50 @@
         <v>#REF!</v>
       </c>
       <c r="N34" s="4" t="e">
-        <f>N5/J5-1</f>
+        <f t="shared" ref="N34:S34" si="24">N5/J5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O34" s="4" t="e">
-        <f>O5/K5-1</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P34" s="141" t="e">
-        <f>P5/L5-1</f>
+      <c r="P34" s="4" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q34" s="4" t="e">
-        <f>Q5/M5-1</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R34" s="4">
-        <f>R5/N5-1</f>
+        <f t="shared" si="24"/>
         <v>3.5541467667348954</v>
       </c>
       <c r="S34" s="7">
-        <f>S5/O5-1</f>
+        <f t="shared" si="24"/>
         <v>0.59019837443173984</v>
       </c>
-      <c r="T34" s="141" t="e">
+      <c r="T34" s="4" t="e">
         <f>T6/P5-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U34" s="141" t="e">
+      <c r="U34" s="4" t="e">
         <f>U6/Q5-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V34" s="157">
+      <c r="V34" s="119">
         <f>V6/R5-1</f>
         <v>1.1640067417133104</v>
       </c>
-      <c r="W34" s="157">
+      <c r="W34" s="119">
         <f>W6/S5-1</f>
         <v>2.995841725683841</v>
       </c>
-      <c r="X34" s="157">
+      <c r="X34" s="119">
         <f>X6/T6-1</f>
         <v>3.1454545454545455</v>
       </c>
-      <c r="Y34" s="157">
+      <c r="Y34" s="119">
         <f>Y6/U6-1</f>
         <v>2.1746031746031744</v>
       </c>
@@ -19921,7 +19912,7 @@
         <f>C10/C5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D35" s="141">
+      <c r="D35" s="4">
         <f>D10/D5</f>
         <v>0.37621265866062659</v>
       </c>
@@ -19934,51 +19925,51 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J35" s="4" t="e">
-        <f>J10/J5</f>
+        <f t="shared" ref="J35:U35" si="25">J10/J5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="4" t="e">
-        <f>K10/K5</f>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L35" s="4" t="e">
-        <f>L10/L5</f>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M35" s="4" t="e">
-        <f>M10/M5</f>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N35" s="4">
-        <f>N10/N5</f>
+        <f t="shared" si="25"/>
         <v>0.47706769767265561</v>
       </c>
       <c r="O35" s="4">
-        <f>O10/O5</f>
+        <f t="shared" si="25"/>
         <v>0.24876015980162555</v>
       </c>
-      <c r="P35" s="141" t="e">
-        <f>P10/P5</f>
+      <c r="P35" s="4" t="e">
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q35" s="4" t="e">
-        <f>Q10/Q5</f>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R35" s="4">
-        <f>R10/R5</f>
+        <f t="shared" si="25"/>
         <v>0.57578809380136919</v>
       </c>
       <c r="S35" s="7">
-        <f>S10/S5</f>
+        <f t="shared" si="25"/>
         <v>0.5455298551101293</v>
       </c>
-      <c r="T35" s="141" t="e">
-        <f>T10/T5</f>
+      <c r="T35" s="4" t="e">
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U35" s="141" t="e">
-        <f>U10/U5</f>
+      <c r="U35" s="4" t="e">
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -19990,7 +19981,7 @@
         <f>C11/C5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D36" s="141">
+      <c r="D36" s="4">
         <f>D11/D5</f>
         <v>0.26961622291550924</v>
       </c>
@@ -20003,51 +19994,51 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J36" s="4" t="e">
-        <f>J11/J5</f>
+        <f t="shared" ref="J36:U36" si="26">J11/J5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="4" t="e">
-        <f>K11/K5</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L36" s="4" t="e">
-        <f>L11/L5</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M36" s="4" t="e">
-        <f>M11/M5</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N36" s="4">
-        <f>N11/N5</f>
+        <f t="shared" si="26"/>
         <v>0.64307103328026671</v>
       </c>
       <c r="O36" s="4">
-        <f>O11/O5</f>
+        <f t="shared" si="26"/>
         <v>0.31062301969968314</v>
       </c>
-      <c r="P36" s="141" t="e">
-        <f>P11/P5</f>
+      <c r="P36" s="4" t="e">
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q36" s="4" t="e">
-        <f>Q11/Q5</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R36" s="4">
-        <f>R11/R5</f>
+        <f t="shared" si="26"/>
         <v>0.35467238186395883</v>
       </c>
       <c r="S36" s="7">
-        <f>S11/S5</f>
+        <f t="shared" si="26"/>
         <v>0.53698048643146423</v>
       </c>
-      <c r="T36" s="141" t="e">
-        <f>T11/T5</f>
+      <c r="T36" s="4" t="e">
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U36" s="141" t="e">
-        <f>U11/U5</f>
+      <c r="U36" s="4" t="e">
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -20059,7 +20050,7 @@
         <f>C15/C5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D37" s="141">
+      <c r="D37" s="4">
         <f>D15/D5</f>
         <v>-8.36574212573187E-3</v>
       </c>
@@ -20072,51 +20063,51 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J37" s="4" t="e">
-        <f>J15/J5</f>
+        <f t="shared" ref="J37:U37" si="27">J15/J5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K37" s="4" t="e">
-        <f>K15/K5</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L37" s="4" t="e">
-        <f>L15/L5</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M37" s="4" t="e">
-        <f>M15/M5</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N37" s="4">
-        <f>N15/N5</f>
+        <f t="shared" si="27"/>
         <v>-3.081646577211735E-2</v>
       </c>
       <c r="O37" s="4">
-        <f>O15/O5</f>
+        <f t="shared" si="27"/>
         <v>-2.6725444276071084E-2</v>
       </c>
-      <c r="P37" s="141" t="e">
-        <f>P15/P5</f>
+      <c r="P37" s="4" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q37" s="4" t="e">
-        <f>Q15/Q5</f>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R37" s="4">
-        <f>R15/R5</f>
+        <f t="shared" si="27"/>
         <v>-1.5930418860151063E-2</v>
       </c>
       <c r="S37" s="7">
-        <f>S15/S5</f>
+        <f t="shared" si="27"/>
         <v>-9.8271717237346495E-3</v>
       </c>
-      <c r="T37" s="141" t="e">
-        <f>T15/T5</f>
+      <c r="T37" s="4" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U37" s="141" t="e">
-        <f>U15/U5</f>
+      <c r="U37" s="4" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -20125,16 +20116,16 @@
         <v>172</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="141" t="e">
-        <f>D3/C3-1</f>
+      <c r="D38" s="4" t="e">
+        <f t="shared" ref="D38:F39" si="28">D3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E38" s="7">
-        <f>E3/D3-1</f>
+        <f t="shared" si="28"/>
         <v>1.6326084948964352</v>
       </c>
       <c r="F38" s="4">
-        <f>F3/E3-1</f>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="J38" s="4"/>
@@ -20143,9 +20134,9 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="P38" s="141"/>
+      <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
-      <c r="R38" s="141">
+      <c r="R38" s="4">
         <f>R3/N3</f>
         <v>4.6989006555723654</v>
       </c>
@@ -20153,24 +20144,24 @@
         <f>S3/O3</f>
         <v>1.4750579381933857</v>
       </c>
-      <c r="T38" s="141"/>
-      <c r="U38" s="141"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>173</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="141" t="e">
-        <f>D4/C4-1</f>
+      <c r="D39" s="4" t="e">
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E39" s="7">
-        <f>E4/D4-1</f>
+        <f t="shared" si="28"/>
         <v>4.2798711755233487</v>
       </c>
       <c r="F39" s="4">
-        <f>F4/E4-1</f>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="J39" s="4"/>
@@ -20179,9 +20170,9 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="P39" s="141"/>
+      <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
-      <c r="R39" s="141">
+      <c r="R39" s="4">
         <f>R4/N4</f>
         <v>2.3038570084666041</v>
       </c>
@@ -20189,8 +20180,8 @@
         <f>S4/O4</f>
         <v>6.5005636978579471</v>
       </c>
-      <c r="T39" s="141"/>
-      <c r="U39" s="141"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
@@ -20201,11 +20192,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D40" s="38" t="e">
-        <f t="shared" ref="D40:E40" si="19">D30/C30-1</f>
+        <f t="shared" ref="D40:E40" si="29">D30/C30-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>-2.3395698513715342</v>
       </c>
       <c r="F40" s="38">
@@ -20233,80 +20224,72 @@
         <v>#REF!</v>
       </c>
       <c r="N40" s="4" t="e">
-        <f t="shared" ref="N40" si="20">N28/J28-1</f>
+        <f t="shared" ref="N40" si="30">N28/J28-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O40" s="4" t="e">
-        <f t="shared" ref="O40" si="21">O28/K28-1</f>
+        <f t="shared" ref="O40" si="31">O28/K28-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P40" s="141" t="e">
-        <f t="shared" ref="P40" si="22">P28/L28-1</f>
+      <c r="P40" s="4" t="e">
+        <f t="shared" ref="P40" si="32">P28/L28-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="4" t="e">
-        <f t="shared" ref="Q40" si="23">Q28/M28-1</f>
+        <f t="shared" ref="Q40" si="33">Q28/M28-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R40" s="4">
-        <f t="shared" ref="R40" si="24">R28/N28-1</f>
+        <f t="shared" ref="R40" si="34">R28/N28-1</f>
         <v>-8.4453327654961505</v>
       </c>
       <c r="S40" s="7">
-        <f t="shared" ref="S40" si="25">S28/O28-1</f>
+        <f t="shared" ref="S40" si="35">S28/O28-1</f>
         <v>6.1001005116959135</v>
       </c>
-      <c r="T40" s="141" t="e">
+      <c r="T40" s="4" t="e">
         <f>T31/P28-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U40" s="141" t="e">
+      <c r="U40" s="4" t="e">
         <f>U31/Q28-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V40" s="157">
+      <c r="V40" s="119">
         <f>V31/R30-1</f>
         <v>-1.0282114078640496</v>
       </c>
-      <c r="W40" s="157">
+      <c r="W40" s="119">
         <f>W31/S30-1</f>
         <v>-1.1342405098869421</v>
       </c>
-      <c r="X40" s="157">
+      <c r="X40" s="119">
         <f>X31/T31-1</f>
         <v>-2.1818181818181817</v>
       </c>
-      <c r="Y40" s="157">
+      <c r="Y40" s="119">
         <f>Y31/U31-1</f>
         <v>-5.1999999999999993</v>
       </c>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="T41" s="135"/>
-      <c r="U41" s="135"/>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="T42" s="135"/>
-      <c r="U42" s="135"/>
     </row>
     <row r="43" spans="2:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C43" s="11">
-        <f t="shared" ref="C43:F43" si="26">C44+C45-C73-C60</f>
+        <f t="shared" ref="C43:F43" si="36">C44+C45-C73-C60</f>
         <v>0</v>
       </c>
-      <c r="D43" s="136">
-        <f t="shared" si="26"/>
+      <c r="D43" s="11">
+        <f t="shared" si="36"/>
         <v>359.14199999999994</v>
       </c>
       <c r="E43" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>421.74099999999987</v>
       </c>
       <c r="F43" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="J43" s="11">
@@ -20322,39 +20305,39 @@
         <v>0</v>
       </c>
       <c r="M43" s="11">
-        <f t="shared" ref="M43:O43" si="27">M44+M45-M73-M60</f>
+        <f t="shared" ref="M43:O43" si="37">M44+M45-M73-M60</f>
         <v>359.14199999999994</v>
       </c>
       <c r="N43" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O43" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="P43" s="136">
-        <f t="shared" ref="P43:S43" si="28">P44+P45-P73-P60</f>
+      <c r="P43" s="11">
+        <f t="shared" ref="P43:S43" si="38">P44+P45-P73-P60</f>
         <v>0</v>
       </c>
       <c r="Q43" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>421.74099999999987</v>
       </c>
       <c r="R43" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>901.89999999999986</v>
       </c>
       <c r="S43" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>2690.1440000000002</v>
       </c>
-      <c r="T43" s="136">
-        <f t="shared" ref="T43:U43" si="29">T44+T45-T73-T60</f>
+      <c r="T43" s="11">
+        <f t="shared" ref="T43:U43" si="39">T44+T45-T73-T60</f>
         <v>0</v>
       </c>
-      <c r="U43" s="136">
-        <f t="shared" si="29"/>
+      <c r="U43" s="11">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
@@ -20363,7 +20346,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="10"/>
-      <c r="D44" s="138">
+      <c r="D44" s="10">
         <v>404.601</v>
       </c>
       <c r="E44" s="15">
@@ -20378,7 +20361,7 @@
       </c>
       <c r="N44" s="10"/>
       <c r="O44" s="10"/>
-      <c r="P44" s="138"/>
+      <c r="P44" s="10"/>
       <c r="Q44" s="10">
         <f>E44</f>
         <v>564.52599999999995</v>
@@ -20389,15 +20372,15 @@
       <c r="S44" s="15">
         <v>3260.5889999999999</v>
       </c>
-      <c r="T44" s="138"/>
-      <c r="U44" s="138"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="10"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>14</v>
       </c>
       <c r="C45" s="10"/>
-      <c r="D45" s="138">
+      <c r="D45" s="10">
         <v>0.152</v>
       </c>
       <c r="E45" s="15">
@@ -20407,14 +20390,14 @@
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
       <c r="M45" s="10">
-        <f t="shared" ref="M45:M50" si="30">D45</f>
+        <f t="shared" ref="M45:M50" si="40">D45</f>
         <v>0.152</v>
       </c>
       <c r="N45" s="10"/>
       <c r="O45" s="10"/>
-      <c r="P45" s="138"/>
+      <c r="P45" s="10"/>
       <c r="Q45" s="10">
-        <f t="shared" ref="Q45:Q50" si="31">E45</f>
+        <f t="shared" ref="Q45:Q50" si="41">E45</f>
         <v>1.5640000000000001</v>
       </c>
       <c r="R45" s="10">
@@ -20423,15 +20406,15 @@
       <c r="S45" s="15">
         <v>9.6059999999999999</v>
       </c>
-      <c r="T45" s="138"/>
-      <c r="U45" s="138"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>139</v>
       </c>
       <c r="C46" s="10"/>
-      <c r="D46" s="138">
+      <c r="D46" s="10">
         <v>11.888</v>
       </c>
       <c r="E46" s="15">
@@ -20441,14 +20424,14 @@
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
       <c r="M46" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>11.888</v>
       </c>
       <c r="N46" s="10"/>
       <c r="O46" s="10"/>
-      <c r="P46" s="138"/>
+      <c r="P46" s="10"/>
       <c r="Q46" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="41"/>
         <v>45.908000000000001</v>
       </c>
       <c r="R46" s="10">
@@ -20457,15 +20440,15 @@
       <c r="S46" s="15">
         <v>55.33</v>
       </c>
-      <c r="T46" s="138"/>
-      <c r="U46" s="138"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10"/>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>140</v>
       </c>
       <c r="C47" s="10"/>
-      <c r="D47" s="148">
+      <c r="D47" s="10">
         <v>0</v>
       </c>
       <c r="E47" s="15">
@@ -20475,29 +20458,29 @@
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
       <c r="M47" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N47" s="10"/>
       <c r="O47" s="10"/>
-      <c r="P47" s="138"/>
+      <c r="P47" s="10"/>
       <c r="Q47" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="41"/>
         <v>5.7560000000000002</v>
       </c>
       <c r="R47" s="10">
         <v>2.91</v>
       </c>
       <c r="S47" s="15"/>
-      <c r="T47" s="138"/>
-      <c r="U47" s="138"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>141</v>
       </c>
       <c r="C48" s="10"/>
-      <c r="D48" s="148">
+      <c r="D48" s="10">
         <v>6.53</v>
       </c>
       <c r="E48" s="15">
@@ -20507,27 +20490,27 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
       <c r="M48" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>6.53</v>
       </c>
       <c r="N48" s="10"/>
       <c r="O48" s="10"/>
-      <c r="P48" s="138"/>
+      <c r="P48" s="10"/>
       <c r="Q48" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="R48" s="10"/>
       <c r="S48" s="15"/>
-      <c r="T48" s="138"/>
-      <c r="U48" s="138"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
     </row>
     <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>142</v>
       </c>
       <c r="C49" s="10"/>
-      <c r="D49" s="148">
+      <c r="D49" s="10">
         <v>0</v>
       </c>
       <c r="E49" s="15">
@@ -20537,29 +20520,29 @@
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
       <c r="M49" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N49" s="10"/>
       <c r="O49" s="10"/>
-      <c r="P49" s="138"/>
+      <c r="P49" s="10"/>
       <c r="Q49" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="41"/>
         <v>2.581</v>
       </c>
       <c r="R49" s="10">
         <v>0</v>
       </c>
       <c r="S49" s="15"/>
-      <c r="T49" s="138"/>
-      <c r="U49" s="138"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
     </row>
     <row r="50" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>143</v>
       </c>
       <c r="C50" s="10"/>
-      <c r="D50" s="148">
+      <c r="D50" s="10">
         <v>29.213999999999999</v>
       </c>
       <c r="E50" s="15">
@@ -20569,14 +20552,14 @@
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
       <c r="M50" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>29.213999999999999</v>
       </c>
       <c r="N50" s="10"/>
       <c r="O50" s="10"/>
-      <c r="P50" s="138"/>
+      <c r="P50" s="10"/>
       <c r="Q50" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="41"/>
         <v>20.838000000000001</v>
       </c>
       <c r="R50" s="10">
@@ -20586,75 +20569,75 @@
         <f>20.102+37.794</f>
         <v>57.896000000000001</v>
       </c>
-      <c r="T50" s="138"/>
-      <c r="U50" s="138"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10"/>
     </row>
     <row r="51" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C51" s="11">
-        <f t="shared" ref="C51" si="32">SUM(C44:C50)</f>
+        <f t="shared" ref="C51" si="42">SUM(C44:C50)</f>
         <v>0</v>
       </c>
-      <c r="D51" s="136">
-        <f t="shared" ref="D51:F51" si="33">SUM(D44:D50)</f>
+      <c r="D51" s="11">
+        <f t="shared" ref="D51:F51" si="43">SUM(D44:D50)</f>
         <v>452.38499999999993</v>
       </c>
       <c r="E51" s="14">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>641.17299999999989</v>
       </c>
       <c r="F51" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J51" s="11">
-        <f t="shared" ref="J51:L51" si="34">SUM(J44:J50)</f>
+        <f t="shared" ref="J51:L51" si="44">SUM(J44:J50)</f>
         <v>0</v>
       </c>
       <c r="K51" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L51" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="M51" s="11">
-        <f t="shared" ref="M51:O51" si="35">SUM(M44:M50)</f>
+        <f t="shared" ref="M51:O51" si="45">SUM(M44:M50)</f>
         <v>452.38499999999993</v>
       </c>
       <c r="N51" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="O51" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="P51" s="136">
-        <f t="shared" ref="P51:S51" si="36">SUM(P44:P50)</f>
+      <c r="P51" s="11">
+        <f t="shared" ref="P51:S51" si="46">SUM(P44:P50)</f>
         <v>0</v>
       </c>
       <c r="Q51" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>641.17299999999989</v>
       </c>
       <c r="R51" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>1123.94</v>
       </c>
       <c r="S51" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>3383.4210000000003</v>
       </c>
-      <c r="T51" s="136">
-        <f t="shared" ref="T51:U51" si="37">SUM(T44:T50)</f>
+      <c r="T51" s="11">
+        <f t="shared" ref="T51:U51" si="47">SUM(T44:T50)</f>
         <v>0</v>
       </c>
-      <c r="U51" s="136">
-        <f t="shared" si="37"/>
+      <c r="U51" s="11">
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
@@ -20663,7 +20646,7 @@
         <v>57</v>
       </c>
       <c r="C52" s="10"/>
-      <c r="D52" s="138">
+      <c r="D52" s="10">
         <v>441.37099999999998</v>
       </c>
       <c r="E52" s="15">
@@ -20674,14 +20657,14 @@
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
       <c r="M52" s="10">
-        <f t="shared" ref="M52:M58" si="38">D52</f>
+        <f t="shared" ref="M52:M58" si="48">D52</f>
         <v>441.37099999999998</v>
       </c>
       <c r="N52" s="10"/>
       <c r="O52" s="10"/>
-      <c r="P52" s="138"/>
+      <c r="P52" s="10"/>
       <c r="Q52" s="10">
-        <f t="shared" ref="Q52:Q58" si="39">E52</f>
+        <f t="shared" ref="Q52:Q58" si="49">E52</f>
         <v>1930.567</v>
       </c>
       <c r="R52" s="10">
@@ -20690,15 +20673,15 @@
       <c r="S52" s="15">
         <v>3170.451</v>
       </c>
-      <c r="T52" s="138"/>
-      <c r="U52" s="138"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
     </row>
     <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="10"/>
-      <c r="D53" s="138"/>
+      <c r="D53" s="10"/>
       <c r="E53" s="15"/>
       <c r="F53" s="10"/>
       <c r="J53" s="10"/>
@@ -20707,21 +20690,21 @@
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
       <c r="O53" s="10"/>
-      <c r="P53" s="138"/>
+      <c r="P53" s="10"/>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
       <c r="S53" s="15">
         <v>107.57299999999999</v>
       </c>
-      <c r="T53" s="138"/>
-      <c r="U53" s="138"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
     </row>
     <row r="54" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>144</v>
       </c>
       <c r="C54" s="10"/>
-      <c r="D54" s="138">
+      <c r="D54" s="10">
         <v>1.3360000000000001</v>
       </c>
       <c r="E54" s="15">
@@ -20732,14 +20715,14 @@
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
       <c r="M54" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>1.3360000000000001</v>
       </c>
       <c r="N54" s="10"/>
       <c r="O54" s="10"/>
-      <c r="P54" s="138"/>
+      <c r="P54" s="10"/>
       <c r="Q54" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>1.4630000000000001</v>
       </c>
       <c r="R54" s="10">
@@ -20748,15 +20731,15 @@
       <c r="S54" s="15">
         <v>1.3280000000000001</v>
       </c>
-      <c r="T54" s="138"/>
-      <c r="U54" s="138"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="10"/>
     </row>
     <row r="55" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>139</v>
       </c>
       <c r="C55" s="10"/>
-      <c r="D55" s="138">
+      <c r="D55" s="10">
         <v>257.3</v>
       </c>
       <c r="E55" s="15">
@@ -20767,14 +20750,14 @@
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
       <c r="M55" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>257.3</v>
       </c>
       <c r="N55" s="10"/>
       <c r="O55" s="10"/>
-      <c r="P55" s="138"/>
+      <c r="P55" s="10"/>
       <c r="Q55" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>32.915999999999997</v>
       </c>
       <c r="R55" s="10">
@@ -20783,15 +20766,15 @@
       <c r="S55" s="15">
         <v>148.822</v>
       </c>
-      <c r="T55" s="138"/>
-      <c r="U55" s="138"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
     </row>
     <row r="56" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>141</v>
       </c>
       <c r="C56" s="10"/>
-      <c r="D56" s="138">
+      <c r="D56" s="10">
         <v>0</v>
       </c>
       <c r="E56" s="15">
@@ -20802,14 +20785,14 @@
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
       <c r="M56" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="N56" s="10"/>
       <c r="O56" s="10"/>
-      <c r="P56" s="138"/>
+      <c r="P56" s="10"/>
       <c r="Q56" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>211.61699999999999</v>
       </c>
       <c r="R56" s="10">
@@ -20818,15 +20801,15 @@
       <c r="S56" s="15">
         <v>0</v>
       </c>
-      <c r="T56" s="138"/>
-      <c r="U56" s="138"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
     </row>
     <row r="57" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>140</v>
       </c>
       <c r="C57" s="10"/>
-      <c r="D57" s="138">
+      <c r="D57" s="10">
         <v>0</v>
       </c>
       <c r="E57" s="15">
@@ -20837,14 +20820,14 @@
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
       <c r="M57" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="N57" s="10"/>
       <c r="O57" s="10"/>
-      <c r="P57" s="138"/>
+      <c r="P57" s="10"/>
       <c r="Q57" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>122.1</v>
       </c>
       <c r="R57" s="10">
@@ -20853,15 +20836,15 @@
       <c r="S57" s="15">
         <v>215.7</v>
       </c>
-      <c r="T57" s="138"/>
-      <c r="U57" s="138"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
     </row>
     <row r="58" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>145</v>
       </c>
       <c r="C58" s="10"/>
-      <c r="D58" s="138">
+      <c r="D58" s="10">
         <v>0.42699999999999999</v>
       </c>
       <c r="E58" s="15">
@@ -20872,14 +20855,14 @@
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
       <c r="M58" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0.42699999999999999</v>
       </c>
       <c r="N58" s="10"/>
       <c r="O58" s="10"/>
-      <c r="P58" s="138"/>
+      <c r="P58" s="10"/>
       <c r="Q58" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0.48599999999999999</v>
       </c>
       <c r="R58" s="10">
@@ -20888,8 +20871,8 @@
       <c r="S58" s="15">
         <v>0.28199999999999997</v>
       </c>
-      <c r="T58" s="138"/>
-      <c r="U58" s="138"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="10"/>
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
@@ -20899,16 +20882,16 @@
         <f>SUM(C51:C58)</f>
         <v>0</v>
       </c>
-      <c r="D59" s="136">
-        <f t="shared" ref="D59:F59" si="40">SUM(D51:D58)</f>
+      <c r="D59" s="11">
+        <f t="shared" ref="D59:F59" si="50">SUM(D51:D58)</f>
         <v>1152.8189999999997</v>
       </c>
       <c r="E59" s="14">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>2940.3220000000001</v>
       </c>
       <c r="F59" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="J59" s="11">
@@ -20924,39 +20907,39 @@
         <v>0</v>
       </c>
       <c r="M59" s="11">
-        <f t="shared" ref="M59:O59" si="41">SUM(M51:M58)</f>
+        <f t="shared" ref="M59:O59" si="51">SUM(M51:M58)</f>
         <v>1152.8189999999997</v>
       </c>
       <c r="N59" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="O59" s="11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="P59" s="136">
-        <f t="shared" ref="P59:S59" si="42">SUM(P51:P58)</f>
+      <c r="P59" s="11">
+        <f t="shared" ref="P59:S59" si="52">SUM(P51:P58)</f>
         <v>0</v>
       </c>
       <c r="Q59" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>2940.3220000000001</v>
       </c>
       <c r="R59" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>4267.3740000000007</v>
       </c>
       <c r="S59" s="14">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>7027.5770000000011</v>
       </c>
-      <c r="T59" s="136">
-        <f t="shared" ref="T59:U59" si="43">SUM(T51:T58)</f>
+      <c r="T59" s="11">
+        <f t="shared" ref="T59:U59" si="53">SUM(T51:T58)</f>
         <v>0</v>
       </c>
-      <c r="U59" s="136">
-        <f t="shared" si="43"/>
+      <c r="U59" s="11">
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
     </row>
@@ -20965,7 +20948,7 @@
         <v>18</v>
       </c>
       <c r="C60" s="10"/>
-      <c r="D60" s="138">
+      <c r="D60" s="10">
         <v>45.494</v>
       </c>
       <c r="E60" s="15">
@@ -20976,14 +20959,14 @@
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
       <c r="M60" s="10">
-        <f t="shared" ref="M60:M65" si="44">D60</f>
+        <f t="shared" ref="M60:M65" si="54">D60</f>
         <v>45.494</v>
       </c>
       <c r="N60" s="10"/>
       <c r="O60" s="10"/>
-      <c r="P60" s="138"/>
+      <c r="P60" s="10"/>
       <c r="Q60" s="10">
-        <f t="shared" ref="Q60:Q65" si="45">E60</f>
+        <f t="shared" ref="Q60:Q65" si="55">E60</f>
         <v>144.11500000000001</v>
       </c>
       <c r="R60" s="10">
@@ -20992,15 +20975,15 @@
       <c r="S60" s="15">
         <v>576.26800000000003</v>
       </c>
-      <c r="T60" s="138"/>
-      <c r="U60" s="138"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="10"/>
     </row>
     <row r="61" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>146</v>
       </c>
       <c r="C61" s="10"/>
-      <c r="D61" s="138">
+      <c r="D61" s="10">
         <v>0.28899999999999998</v>
       </c>
       <c r="E61" s="15">
@@ -21011,14 +20994,14 @@
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
       <c r="M61" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>0.28899999999999998</v>
       </c>
       <c r="N61" s="10"/>
       <c r="O61" s="10"/>
-      <c r="P61" s="138"/>
+      <c r="P61" s="10"/>
       <c r="Q61" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.40400000000000003</v>
       </c>
       <c r="R61" s="10">
@@ -21027,15 +21010,15 @@
       <c r="S61" s="15">
         <v>0.40200000000000002</v>
       </c>
-      <c r="T61" s="138"/>
-      <c r="U61" s="138"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>171</v>
       </c>
       <c r="C62" s="10"/>
-      <c r="D62" s="138"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="15"/>
       <c r="F62" s="10"/>
       <c r="J62" s="10"/>
@@ -21044,21 +21027,21 @@
       <c r="M62" s="10"/>
       <c r="N62" s="10"/>
       <c r="O62" s="10"/>
-      <c r="P62" s="138"/>
+      <c r="P62" s="10"/>
       <c r="Q62" s="10"/>
       <c r="R62" s="10"/>
       <c r="S62" s="15">
         <v>61.853999999999999</v>
       </c>
-      <c r="T62" s="138"/>
-      <c r="U62" s="138"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>147</v>
       </c>
       <c r="C63" s="10"/>
-      <c r="D63" s="138">
+      <c r="D63" s="10">
         <v>1.389</v>
       </c>
       <c r="E63" s="15">
@@ -21069,14 +21052,14 @@
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
       <c r="M63" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>1.389</v>
       </c>
       <c r="N63" s="10"/>
       <c r="O63" s="10"/>
-      <c r="P63" s="138"/>
+      <c r="P63" s="10"/>
       <c r="Q63" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="R63" s="10">
@@ -21085,15 +21068,15 @@
       <c r="S63" s="15">
         <v>0.752</v>
       </c>
-      <c r="T63" s="138"/>
-      <c r="U63" s="138"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>148</v>
       </c>
       <c r="C64" s="10"/>
-      <c r="D64" s="138">
+      <c r="D64" s="10">
         <v>2.5579999999999998</v>
       </c>
       <c r="E64" s="15">
@@ -21104,14 +21087,14 @@
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
       <c r="M64" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>2.5579999999999998</v>
       </c>
       <c r="N64" s="10"/>
       <c r="O64" s="10"/>
-      <c r="P64" s="138"/>
+      <c r="P64" s="10"/>
       <c r="Q64" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>0.88400000000000001</v>
       </c>
       <c r="R64" s="10">
@@ -21120,15 +21103,15 @@
       <c r="S64" s="15">
         <v>6.7939999999999996</v>
       </c>
-      <c r="T64" s="138"/>
-      <c r="U64" s="138"/>
+      <c r="T64" s="10"/>
+      <c r="U64" s="10"/>
     </row>
     <row r="65" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>149</v>
       </c>
       <c r="C65" s="10"/>
-      <c r="D65" s="138">
+      <c r="D65" s="10">
         <v>1.3420000000000001</v>
       </c>
       <c r="E65" s="15">
@@ -21139,14 +21122,14 @@
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
       <c r="M65" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>1.3420000000000001</v>
       </c>
       <c r="N65" s="10"/>
       <c r="O65" s="10"/>
-      <c r="P65" s="138"/>
+      <c r="P65" s="10"/>
       <c r="Q65" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>3.9449999999999998</v>
       </c>
       <c r="R65" s="10">
@@ -21155,8 +21138,8 @@
       <c r="S65" s="15">
         <v>36.061</v>
       </c>
-      <c r="T65" s="138"/>
-      <c r="U65" s="138"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
@@ -21166,16 +21149,16 @@
         <f>SUM(C60:C65)</f>
         <v>0</v>
       </c>
-      <c r="D66" s="136">
-        <f t="shared" ref="D66:F66" si="46">SUM(D60:D65)</f>
+      <c r="D66" s="11">
+        <f t="shared" ref="D66:F66" si="56">SUM(D60:D65)</f>
         <v>51.072000000000003</v>
       </c>
       <c r="E66" s="14">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>149.34799999999998</v>
       </c>
       <c r="F66" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="J66" s="11">
@@ -21191,39 +21174,39 @@
         <v>0</v>
       </c>
       <c r="M66" s="11">
-        <f t="shared" ref="M66:O66" si="47">SUM(M60:M65)</f>
+        <f t="shared" ref="M66:O66" si="57">SUM(M60:M65)</f>
         <v>51.072000000000003</v>
       </c>
       <c r="N66" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="O66" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="P66" s="136">
-        <f t="shared" ref="P66:S66" si="48">SUM(P60:P65)</f>
+      <c r="P66" s="11">
+        <f t="shared" ref="P66:S66" si="58">SUM(P60:P65)</f>
         <v>0</v>
       </c>
       <c r="Q66" s="11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>149.34799999999998</v>
       </c>
       <c r="R66" s="11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>203.74499999999998</v>
       </c>
       <c r="S66" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>682.13100000000009</v>
       </c>
-      <c r="T66" s="136">
-        <f t="shared" ref="T66:U66" si="49">SUM(T60:T65)</f>
+      <c r="T66" s="11">
+        <f t="shared" ref="T66:U66" si="59">SUM(T60:T65)</f>
         <v>0</v>
       </c>
-      <c r="U66" s="136">
-        <f t="shared" si="49"/>
+      <c r="U66" s="11">
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
     </row>
@@ -21232,7 +21215,7 @@
         <v>144</v>
       </c>
       <c r="C67" s="10"/>
-      <c r="D67" s="138">
+      <c r="D67" s="10">
         <v>1.032</v>
       </c>
       <c r="E67" s="15">
@@ -21243,14 +21226,14 @@
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
       <c r="M67" s="10">
-        <f t="shared" ref="M67:M73" si="50">D67</f>
+        <f t="shared" ref="M67:M73" si="60">D67</f>
         <v>1.032</v>
       </c>
       <c r="N67" s="10"/>
       <c r="O67" s="10"/>
-      <c r="P67" s="138"/>
+      <c r="P67" s="10"/>
       <c r="Q67" s="10">
-        <f t="shared" ref="Q67:Q73" si="51">E67</f>
+        <f t="shared" ref="Q67:Q73" si="61">E67</f>
         <v>1.0629999999999999</v>
       </c>
       <c r="R67" s="10">
@@ -21259,15 +21242,15 @@
       <c r="S67" s="15">
         <v>0.93600000000000005</v>
       </c>
-      <c r="T67" s="138"/>
-      <c r="U67" s="138"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="10"/>
     </row>
     <row r="68" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>171</v>
       </c>
       <c r="C68" s="10"/>
-      <c r="D68" s="138"/>
+      <c r="D68" s="10"/>
       <c r="E68" s="15"/>
       <c r="F68" s="10"/>
       <c r="J68" s="10"/>
@@ -21276,21 +21259,21 @@
       <c r="M68" s="10"/>
       <c r="N68" s="10"/>
       <c r="O68" s="10"/>
-      <c r="P68" s="138"/>
+      <c r="P68" s="10"/>
       <c r="Q68" s="10"/>
       <c r="R68" s="10"/>
       <c r="S68" s="15">
         <v>94.06</v>
       </c>
-      <c r="T68" s="138"/>
-      <c r="U68" s="138"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="10"/>
     </row>
     <row r="69" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>150</v>
       </c>
       <c r="C69" s="10"/>
-      <c r="D69" s="138">
+      <c r="D69" s="10">
         <v>0</v>
       </c>
       <c r="E69" s="15">
@@ -21301,14 +21284,14 @@
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
       <c r="M69" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="N69" s="10"/>
       <c r="O69" s="10"/>
-      <c r="P69" s="138"/>
+      <c r="P69" s="10"/>
       <c r="Q69" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>962.76499999999999</v>
       </c>
       <c r="R69" s="10">
@@ -21317,15 +21300,15 @@
       <c r="S69" s="15">
         <v>3685.2959999999998</v>
       </c>
-      <c r="T69" s="138"/>
-      <c r="U69" s="138"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
     </row>
     <row r="70" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>148</v>
       </c>
       <c r="C70" s="10"/>
-      <c r="D70" s="138"/>
+      <c r="D70" s="10"/>
       <c r="E70" s="15"/>
       <c r="F70" s="10"/>
       <c r="J70" s="10"/>
@@ -21334,7 +21317,7 @@
       <c r="M70" s="10"/>
       <c r="N70" s="10"/>
       <c r="O70" s="10"/>
-      <c r="P70" s="138"/>
+      <c r="P70" s="10"/>
       <c r="Q70" s="10"/>
       <c r="R70" s="10">
         <v>22.234000000000002</v>
@@ -21342,15 +21325,15 @@
       <c r="S70" s="15">
         <v>39.831000000000003</v>
       </c>
-      <c r="T70" s="138"/>
-      <c r="U70" s="138"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="10"/>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>151</v>
       </c>
       <c r="C71" s="10"/>
-      <c r="D71" s="138">
+      <c r="D71" s="10">
         <v>3.125</v>
       </c>
       <c r="E71" s="15">
@@ -21361,14 +21344,14 @@
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
       <c r="M71" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>3.125</v>
       </c>
       <c r="N71" s="10"/>
       <c r="O71" s="10"/>
-      <c r="P71" s="138"/>
+      <c r="P71" s="10"/>
       <c r="Q71" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>7.9710000000000001</v>
       </c>
       <c r="R71" s="10">
@@ -21377,15 +21360,15 @@
       <c r="S71" s="15">
         <v>8.0549999999999997</v>
       </c>
-      <c r="T71" s="138"/>
-      <c r="U71" s="138"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
     </row>
     <row r="72" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>152</v>
       </c>
       <c r="C72" s="10"/>
-      <c r="D72" s="138">
+      <c r="D72" s="10">
         <v>0</v>
       </c>
       <c r="E72" s="15">
@@ -21396,14 +21379,14 @@
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
       <c r="M72" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="N72" s="10"/>
       <c r="O72" s="10"/>
-      <c r="P72" s="138"/>
+      <c r="P72" s="10"/>
       <c r="Q72" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>1.454</v>
       </c>
       <c r="R72" s="10">
@@ -21412,15 +21395,15 @@
       <c r="S72" s="15">
         <v>2.2919999999999998</v>
       </c>
-      <c r="T72" s="138"/>
-      <c r="U72" s="138"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="10"/>
     </row>
     <row r="73" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>149</v>
       </c>
       <c r="C73" s="10"/>
-      <c r="D73" s="138">
+      <c r="D73" s="10">
         <v>0.11700000000000001</v>
       </c>
       <c r="E73" s="15">
@@ -21431,14 +21414,14 @@
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
       <c r="M73" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>0.11700000000000001</v>
       </c>
       <c r="N73" s="10"/>
       <c r="O73" s="10"/>
-      <c r="P73" s="138"/>
+      <c r="P73" s="10"/>
       <c r="Q73" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>0.23400000000000001</v>
       </c>
       <c r="R73" s="10">
@@ -21447,8 +21430,8 @@
       <c r="S73" s="15">
         <v>3.7829999999999999</v>
       </c>
-      <c r="T73" s="138"/>
-      <c r="U73" s="138"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
@@ -21458,16 +21441,16 @@
         <f>SUM(C66:C73)</f>
         <v>0</v>
       </c>
-      <c r="D74" s="136">
-        <f t="shared" ref="D74:F74" si="52">SUM(D66:D73)</f>
+      <c r="D74" s="11">
+        <f t="shared" ref="D74:F74" si="62">SUM(D66:D73)</f>
         <v>55.345999999999997</v>
       </c>
       <c r="E74" s="14">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>1122.8349999999998</v>
       </c>
       <c r="F74" s="11">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="J74" s="11">
@@ -21483,39 +21466,39 @@
         <v>0</v>
       </c>
       <c r="M74" s="11">
-        <f t="shared" ref="M74:O74" si="53">SUM(M66:M73)</f>
+        <f t="shared" ref="M74:O74" si="63">SUM(M66:M73)</f>
         <v>55.345999999999997</v>
       </c>
       <c r="N74" s="11">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="O74" s="11">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
-      <c r="P74" s="136">
-        <f t="shared" ref="P74:S74" si="54">SUM(P66:P73)</f>
+      <c r="P74" s="11">
+        <f t="shared" ref="P74:S74" si="64">SUM(P66:P73)</f>
         <v>0</v>
       </c>
       <c r="Q74" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>1122.8349999999998</v>
       </c>
       <c r="R74" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>1391.2369999999999</v>
       </c>
       <c r="S74" s="14">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>4516.3840000000009</v>
       </c>
-      <c r="T74" s="136">
-        <f t="shared" ref="T74:U74" si="55">SUM(T66:T73)</f>
+      <c r="T74" s="11">
+        <f t="shared" ref="T74:U74" si="65">SUM(T66:T73)</f>
         <v>0</v>
       </c>
-      <c r="U74" s="136">
-        <f t="shared" si="55"/>
+      <c r="U74" s="11">
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
     </row>
@@ -21527,16 +21510,16 @@
         <f>C59-C74</f>
         <v>0</v>
       </c>
-      <c r="D75" s="138">
-        <f t="shared" ref="D75:F75" si="56">D59-D74</f>
+      <c r="D75" s="10">
+        <f t="shared" ref="D75:F75" si="66">D59-D74</f>
         <v>1097.4729999999997</v>
       </c>
       <c r="E75" s="15">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>1817.4870000000003</v>
       </c>
       <c r="F75" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="J75" s="10">
@@ -21552,39 +21535,39 @@
         <v>0</v>
       </c>
       <c r="M75" s="10">
-        <f t="shared" ref="M75:O75" si="57">M59-M74</f>
+        <f t="shared" ref="M75:O75" si="67">M59-M74</f>
         <v>1097.4729999999997</v>
       </c>
       <c r="N75" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="O75" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
-      <c r="P75" s="138">
-        <f t="shared" ref="P75:S75" si="58">P59-P74</f>
+      <c r="P75" s="10">
+        <f t="shared" ref="P75:S75" si="68">P59-P74</f>
         <v>0</v>
       </c>
       <c r="Q75" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>1817.4870000000003</v>
       </c>
       <c r="R75" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>2876.1370000000006</v>
       </c>
       <c r="S75" s="15">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>2511.1930000000002</v>
       </c>
-      <c r="T75" s="138">
-        <f t="shared" ref="T75:U75" si="59">T59-T74</f>
+      <c r="T75" s="10">
+        <f t="shared" ref="T75:U75" si="69">T59-T74</f>
         <v>0</v>
       </c>
-      <c r="U75" s="138">
-        <f t="shared" si="59"/>
+      <c r="U75" s="10">
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
     </row>
@@ -21593,21 +21576,15 @@
         <v>60</v>
       </c>
       <c r="C77" s="114"/>
-      <c r="D77" s="142"/>
       <c r="E77" s="16"/>
-      <c r="P77" s="142"/>
       <c r="S77" s="16"/>
     </row>
-    <row r="95" spans="4:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="143"/>
+    <row r="95" spans="5:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E95" s="40"/>
-      <c r="P95" s="143"/>
       <c r="S95" s="40"/>
     </row>
-    <row r="96" spans="4:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="142"/>
+    <row r="96" spans="5:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E96" s="16"/>
-      <c r="P96" s="142"/>
       <c r="S96" s="16"/>
     </row>
   </sheetData>
@@ -31124,14 +31101,14 @@
       <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="125" t="s">
+      <c r="H1" s="130" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="127"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="132"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
@@ -31634,10 +31611,10 @@
         <f t="shared" si="0"/>
         <v>-1.9716361120719506E-2</v>
       </c>
-      <c r="H17" s="128" t="s">
+      <c r="H17" s="133" t="s">
         <v>112</v>
       </c>
-      <c r="I17" s="129"/>
+      <c r="I17" s="134"/>
       <c r="M17" s="71"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
@@ -31651,8 +31628,8 @@
         <f t="shared" si="0"/>
         <v>0.25613730175972194</v>
       </c>
-      <c r="H18" s="130"/>
-      <c r="I18" s="131"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="136"/>
       <c r="M18" s="71"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
@@ -32225,14 +32202,14 @@
         <f t="shared" si="0"/>
         <v>-1.2263099219621099E-2</v>
       </c>
-      <c r="H43" s="132" t="s">
+      <c r="H43" s="137" t="s">
         <v>106</v>
       </c>
-      <c r="I43" s="133"/>
-      <c r="J43" s="133"/>
-      <c r="K43" s="133"/>
-      <c r="L43" s="133"/>
-      <c r="M43" s="134"/>
+      <c r="I43" s="138"/>
+      <c r="J43" s="138"/>
+      <c r="K43" s="138"/>
+      <c r="L43" s="138"/>
+      <c r="M43" s="139"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="17" t="s">
@@ -34386,7 +34363,7 @@
         <v>4.83</v>
       </c>
       <c r="D195" s="3">
-        <f t="shared" ref="D195:D235" si="12">C195/C196-1</f>
+        <f t="shared" ref="D195:D234" si="12">C195/C196-1</f>
         <v>-4.3564356435643492E-2</v>
       </c>
     </row>

--- a/Business - Technology Services/Datacenter/IREN.xlsx
+++ b/Business - Technology Services/Datacenter/IREN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\Business - Technology Services\Datacenter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7161583A-C58C-49E3-8DB1-3E7407DED8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96991BB-DCE0-44CC-9146-8F354D786057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
